--- a/光伏配储项目/电价数据/2026/后龙站.xlsx
+++ b/光伏配储项目/电价数据/2026/后龙站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51063</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7873300000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.59005</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.61521</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52062</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51314</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43752</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44095</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42067</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44404</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.24114</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12753</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10354</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11755</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10575</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.08377</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.15683</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.20496</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.15103</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.01173</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09117</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.12598</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04618999999999999</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.22939</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.20392</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23816</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00929</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15671</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.2155</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20679</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.45265</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.71589</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.50257</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5637000000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.32017</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.65704</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.50647</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.47947</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57939</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47527</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.63583</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.82357</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64837</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.64537</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.79432</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.13658</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.44687</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68889</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58575</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.80848</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.60463</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.5996699999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6520900000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.62397</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47812</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47762</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42562</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70735</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.53772</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7575</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.34009</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.80433</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52828</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5187999999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51064</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48921</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41911</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59711</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.69964</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43137</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.52208</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06594</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.49275</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.49528</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.47955</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.49541</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.45479</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.48243</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.52534</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.73886</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.28883</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39541</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.62273</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.05166</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5215599999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.45438</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.49549</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.51464</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.53434</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.48884</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.43299</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.6202799999999999</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7537200000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.61349</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.7032</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.76506</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.73853</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.6288400000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.56537</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7563099999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.5733400000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.5588099999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.0092</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.47985</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.5915499999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.68798</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.47394</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.46712</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.48981</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.45312</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33455</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5120399999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.90735</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.77058</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42636</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.58377</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.46706</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.48731</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47382</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.48605</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.42185</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.21898</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.82801</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.87421</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21752</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.42343</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26791</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47949</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.43161</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52659</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49164</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16967</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42875</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5210199999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43257</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.38429</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5621799999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6379400000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.70657</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.49555</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.52581</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.47585</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45129</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47214</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45819</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41632</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.43986</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34241</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4589</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22876</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.26578</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.4968</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.52585</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.57365</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.61699</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.49671</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.15234</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.09555</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.46135</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.26964</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.79101</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07189</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.20503</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.26333</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23332</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24859</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21946</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.28154</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13238</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.61194</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46843</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29964</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.40828</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04399</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.12456</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.14039</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04457</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04583</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.08623</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04665999999999999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.0344</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04825</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04267</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.0427</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04228</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04234</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04242</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04186</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04249</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04182</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04169</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04511</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21852</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04527</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05136</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05597</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04993</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.03451</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02204</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.04437</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.23629</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.14138</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.18214</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35086</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.7681</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44615</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04328</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04385</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10326</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00192</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04439</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04313</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04323</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04313</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04516</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04406</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04364</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04448</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04954</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04763000000000001</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14299</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33565</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3179</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17257</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17112</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14786</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15959</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15876</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23642</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21418</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22673</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27182</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42798</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45459</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15637</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5077200000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909400000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49803</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78107</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9205099999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49464</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91608</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8678899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29932</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89288</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6326499999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19241</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8714500000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54516</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33624</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03665</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53613</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7954600000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78111</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8773300000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87622</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49735</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40534</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21244</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87905</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55115</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62726</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5396799999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4992799999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43814</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41479</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43378</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58651</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60238</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6686799999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47326</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58158</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45239</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88195</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63466</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9562</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.93832</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86491</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.48998</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6578099999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45237</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35344</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9243899999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46699</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47762</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16571</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26254</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19913</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19876</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27848</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43537</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5966399999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.38283</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.18112</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71517</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8111699999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66498</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59251</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45657</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45609</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5089</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44563</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.44306</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50891</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.44049</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45657</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40422</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.50618</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.5590900000000001</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.94668</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.5751900000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25315</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.91911</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.50739</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.49029</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.6385700000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26427</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41244</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57928</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46795</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.79275</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.47183</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43726</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42177</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32397</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42614</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.54957</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.50954</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.52306</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.49756</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.25517</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.26269</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.26609</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.18192</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.24762</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.18188</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.24376</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.23189</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.4402799999999999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.22716</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.47457</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.24654</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25348</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.48957</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.43617</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.44408</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.43849</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.46272</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.49541</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.48388</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.6742</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38253</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45357</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4477</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44357</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44287</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44832</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34877</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54771</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47503</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42824</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27163</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26454</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24868</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24145</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25308</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27481</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24053</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.20383</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.13774</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.23713</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.17279</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.2288</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42091</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36144</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.40783</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.5565099999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43765</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45371</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.07407999999999999</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25009</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.42483</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.19485</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.23077</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26188</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28547</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.46912</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45317</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70566</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5171</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26176</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28694</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.50505</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34954</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6444800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7981699999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44464</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4618</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34134</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14184</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28474</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20066</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26152</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28076</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22319</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27576</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28065</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14504</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.70641</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59101</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.41708</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6825399999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7662</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46811</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4137</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35999</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49003</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5247999999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47651</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4839</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40969</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40088</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41791</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40079</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45549</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56632</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50783</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45576</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.25436</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44526</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47823</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43466</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46763</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46822</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.58278</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.44622</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.43411</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6497000000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.17164</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44312</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49958</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44319</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.52047</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50276</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.59939</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70241</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.70535</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8102999999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58304</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5131100000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.79611</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7388400000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62407</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66043</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47815</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47357</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47736</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46015</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55098</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42631</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44932</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38653</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21414</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40469</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46045</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11711</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18076</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45241</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40877</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36533</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27923</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23069</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25055</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25372</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04321</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25122</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.1708</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18332</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22905</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26694</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23252</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35006</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26576</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25198</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17237</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21409</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24614</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01838</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11867</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01206</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03907</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01106</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03663</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03293</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04724</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04663</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02322</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02258</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.15065</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04914</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04892000000000001</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00106</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04893</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03116</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04885</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04186</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18506</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24242</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27179</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27551</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28689</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.16303</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.6176200000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.19138</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.28689</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.26165</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.25311</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23738</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25603</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2789700000000001</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.18809</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.67599</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.67091</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6850700000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.6265499999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.18522</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11974</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24722</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.14357</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14962</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.10931</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23398</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.13354</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04521</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.07293999999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.12229</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18846</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02289</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.14287</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.15165</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.16591</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.00774</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.12552</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.13625</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.13512</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16971</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25864</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.44712</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32342</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5604600000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5325800000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.43295</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.45316</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43832</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44621</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46067</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32723</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.57101</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.54449</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49504</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26306</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.27969</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48151</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.49003</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45259</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46804</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5819299999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.47166</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.60019</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.44344</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.25491</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36405</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48111</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.45748</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.46397</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40394</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.49289</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.46078</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4391</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43445</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50246</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5686599999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5694900000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.44799</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5277000000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49702</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5340499999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.47277</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51923</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.4796</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.54212</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7773</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55257</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5565800000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.43173</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36922</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26445</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24271</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17011</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07105</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20657</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.03823</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.2165</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17405</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.00708</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26445</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16887</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06322999999999999</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.0559</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07578</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17365</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08355</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06068</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18178</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15824</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17786</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26257</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4246</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40995</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42179</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42508</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36299</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.84377</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47124</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43278</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28814</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26434</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11659</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.009699999999999999</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03876</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03285</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00548</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01883</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04598</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01778</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02005</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16305</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04542</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24864</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.17283</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.27004</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48978</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40746</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.54557</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.25856</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36419</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5764600000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44747</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23916</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14902</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21594</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24385</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11909</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15779</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.02417</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04718</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04720000000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04623</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04449</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08123999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02856</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06448000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.10002</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17915</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20618</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12578</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.24096</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12911</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.06085</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15439</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.12159</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24378</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19473</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.25092</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25609</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21267</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25498</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45909</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3735</v>
       </c>
     </row>
   </sheetData>
